--- a/tests/mung/fixtures/ratio_z1_2026-07-06.xlsx
+++ b/tests/mung/fixtures/ratio_z1_2026-07-06.xlsx
@@ -104,10 +104,10 @@
     <t>concept_nm</t>
   </si>
   <si>
+    <t>value_num</t>
+  </si>
+  <si>
     <t>value_den</t>
-  </si>
-  <si>
-    <t>value_num</t>
   </si>
   <si>
     <t>value_ratio</t>
@@ -217,10 +217,10 @@
     <tableColumn id="2" name="pertype" dataDxfId="0"/>
     <tableColumn id="3" name="period" dataDxfId="0"/>
     <tableColumn id="4" name="concept_ratio" dataDxfId="0"/>
-    <tableColumn id="5" name="value_den" dataDxfId="1"/>
-    <tableColumn id="6" name="value_num" dataDxfId="1"/>
-    <tableColumn id="7" name="concept_num" dataDxfId="0"/>
-    <tableColumn id="8" name="concept_den" dataDxfId="0"/>
+    <tableColumn id="5" name="concept_num" dataDxfId="0"/>
+    <tableColumn id="6" name="concept_den" dataDxfId="0"/>
+    <tableColumn id="7" name="value_num" dataDxfId="1"/>
+    <tableColumn id="8" name="value_den" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -234,10 +234,10 @@
     <tableColumn id="2" name="pertype" dataDxfId="0"/>
     <tableColumn id="3" name="period" dataDxfId="0"/>
     <tableColumn id="4" name="concept_ratio" dataDxfId="0"/>
-    <tableColumn id="5" name="value_den" dataDxfId="1"/>
-    <tableColumn id="6" name="value_num" dataDxfId="1"/>
-    <tableColumn id="7" name="concept_num" dataDxfId="0"/>
-    <tableColumn id="8" name="concept_den" dataDxfId="0"/>
+    <tableColumn id="5" name="concept_num" dataDxfId="0"/>
+    <tableColumn id="6" name="concept_den" dataDxfId="0"/>
+    <tableColumn id="7" name="value_num" dataDxfId="1"/>
+    <tableColumn id="8" name="value_den" dataDxfId="1"/>
     <tableColumn id="9" name="value_ratio" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1177,16 +1177,16 @@
         <v>17</v>
       </c>
       <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1202,17 +1202,17 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>300</v>
+      </c>
+      <c r="H2" s="2">
         <v>175</v>
-      </c>
-      <c r="F2" s="2">
-        <v>300</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1228,17 +1228,17 @@
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H3" s="2">
         <v>175</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1254,17 +1254,17 @@
       <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2">
+        <v>150</v>
+      </c>
+      <c r="H4" s="2">
         <v>1000</v>
-      </c>
-      <c r="F4" s="2">
-        <v>150</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1280,17 +1280,17 @@
       <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
+        <v>150</v>
+      </c>
+      <c r="H5" s="2">
         <v>1150</v>
-      </c>
-      <c r="F5" s="2">
-        <v>150</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1306,17 +1306,17 @@
       <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="2">
         <v>300</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1332,17 +1332,17 @@
       <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="2">
         <v>1150</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1358,17 +1358,17 @@
       <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2">
+        <v>120</v>
+      </c>
+      <c r="H8" s="2">
         <v>1100</v>
-      </c>
-      <c r="F8" s="2">
-        <v>120</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1384,17 +1384,17 @@
       <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2">
+        <v>120</v>
+      </c>
+      <c r="H9" s="2">
         <v>1000</v>
-      </c>
-      <c r="F9" s="2">
-        <v>120</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1410,17 +1410,17 @@
       <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1100</v>
+      </c>
+      <c r="H10" s="2">
         <v>1000</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1436,16 +1436,16 @@
       <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2">
         <v>1100</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
@@ -1460,16 +1460,16 @@
       <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="E12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
         <v>1100</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
@@ -1484,17 +1484,17 @@
       <c r="D13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>50</v>
+      </c>
+      <c r="H13" s="2">
         <v>40</v>
-      </c>
-      <c r="F13" s="2">
-        <v>50</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1510,17 +1510,17 @@
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
+        <v>275</v>
+      </c>
+      <c r="H14" s="2">
         <v>40</v>
-      </c>
-      <c r="F14" s="2">
-        <v>275</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1536,17 +1536,17 @@
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2">
+        <v>275</v>
+      </c>
+      <c r="H15" s="2">
         <v>50</v>
-      </c>
-      <c r="F15" s="2">
-        <v>275</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1562,16 +1562,16 @@
       <c r="D16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2">
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2">
         <v>275</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
@@ -1586,15 +1586,15 @@
       <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2">
         <v>275</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1610,16 +1610,16 @@
       <c r="D18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2">
+      <c r="E18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2">
         <v>0</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
@@ -1634,16 +1634,16 @@
       <c r="D19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2">
+      <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2">
         <v>0</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
@@ -1658,17 +1658,17 @@
       <c r="D20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="2">
+        <v>150</v>
+      </c>
+      <c r="H20" s="2">
         <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>150</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1684,17 +1684,17 @@
       <c r="D21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="2">
+        <v>150</v>
+      </c>
+      <c r="H21" s="2">
         <v>1150</v>
-      </c>
-      <c r="F21" s="2">
-        <v>150</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1710,17 +1710,17 @@
       <c r="D22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2">
         <v>0</v>
       </c>
-      <c r="F22" s="2">
+      <c r="H22" s="2">
         <v>0</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1736,17 +1736,17 @@
       <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
         <v>1150</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1762,17 +1762,17 @@
       <c r="D24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2">
         <v>1E-07</v>
       </c>
-      <c r="F24" s="2">
+      <c r="H24" s="2">
         <v>1E-07</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1788,17 +1788,17 @@
       <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1E-07</v>
+      </c>
+      <c r="H25" s="2">
         <v>1000</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1E-07</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1814,17 +1814,17 @@
       <c r="D26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1E-07</v>
+      </c>
+      <c r="H26" s="2">
         <v>1000</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1E-07</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1840,16 +1840,16 @@
       <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2">
+      <c r="E27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2">
         <v>1E-07</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
@@ -1864,16 +1864,16 @@
       <c r="D28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2">
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
         <v>1E-07</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
@@ -1888,17 +1888,17 @@
       <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
         <v>160</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1914,15 +1914,15 @@
       <c r="D30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2">
         <v>160</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1938,15 +1938,15 @@
       <c r="D31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2">
         <v>0</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1976,16 +1976,16 @@
         <v>17</v>
       </c>
       <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>19</v>
       </c>
       <c r="I1" t="s">
         <v>30</v>
@@ -2004,17 +2004,17 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>300</v>
+      </c>
+      <c r="H2" s="2">
         <v>175</v>
-      </c>
-      <c r="F2" s="2">
-        <v>300</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="I2" s="2">
         <v>1.714285714285714</v>
@@ -2033,17 +2033,17 @@
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H3" s="2">
         <v>175</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="I3" s="2">
         <v>5.714285714285714</v>
@@ -2062,17 +2062,17 @@
       <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2">
+        <v>150</v>
+      </c>
+      <c r="H4" s="2">
         <v>1000</v>
-      </c>
-      <c r="F4" s="2">
-        <v>150</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="I4" s="2">
         <v>0.15</v>
@@ -2091,17 +2091,17 @@
       <c r="D5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2">
+        <v>150</v>
+      </c>
+      <c r="H5" s="2">
         <v>1150</v>
-      </c>
-      <c r="F5" s="2">
-        <v>150</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I5" s="2">
         <v>0.1304347826086956</v>
@@ -2120,17 +2120,17 @@
       <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="2">
         <v>300</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="I6" s="2">
         <v>3.333333333333333</v>
@@ -2149,17 +2149,17 @@
       <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="2">
         <v>1150</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I7" s="2">
         <v>0.8695652173913043</v>
@@ -2178,17 +2178,17 @@
       <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2">
+        <v>120</v>
+      </c>
+      <c r="H8" s="2">
         <v>1100</v>
-      </c>
-      <c r="F8" s="2">
-        <v>120</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="I8" s="2">
         <v>0.1090909090909091</v>
@@ -2207,17 +2207,17 @@
       <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2">
+        <v>120</v>
+      </c>
+      <c r="H9" s="2">
         <v>1000</v>
-      </c>
-      <c r="F9" s="2">
-        <v>120</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I9" s="2">
         <v>0.12</v>
@@ -2236,17 +2236,17 @@
       <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1100</v>
+      </c>
+      <c r="H10" s="2">
         <v>1000</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1100</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I10" s="2">
         <v>1.1</v>
@@ -2265,16 +2265,16 @@
       <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2">
+      <c r="E11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2">
         <v>1100</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9">
@@ -2290,16 +2290,16 @@
       <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2">
+      <c r="E12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
         <v>1100</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
@@ -2315,17 +2315,17 @@
       <c r="D13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2">
+        <v>50</v>
+      </c>
+      <c r="H13" s="2">
         <v>40</v>
-      </c>
-      <c r="F13" s="2">
-        <v>50</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="I13" s="2">
         <v>1.25</v>
@@ -2344,17 +2344,17 @@
       <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
+        <v>275</v>
+      </c>
+      <c r="H14" s="2">
         <v>40</v>
-      </c>
-      <c r="F14" s="2">
-        <v>275</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="I14" s="2">
         <v>6.875</v>
@@ -2373,17 +2373,17 @@
       <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2">
+        <v>275</v>
+      </c>
+      <c r="H15" s="2">
         <v>50</v>
-      </c>
-      <c r="F15" s="2">
-        <v>275</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="I15" s="2">
         <v>5.5</v>
@@ -2402,16 +2402,16 @@
       <c r="D16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2">
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2">
         <v>275</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9">
@@ -2427,15 +2427,15 @@
       <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2">
         <v>275</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="I17" s="2"/>
     </row>
@@ -2452,16 +2452,16 @@
       <c r="D18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2">
+      <c r="E18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2">
         <v>0</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9">
@@ -2477,16 +2477,16 @@
       <c r="D19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2">
+      <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2">
         <v>0</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9">
@@ -2502,17 +2502,17 @@
       <c r="D20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="2">
+        <v>150</v>
+      </c>
+      <c r="H20" s="2">
         <v>0</v>
-      </c>
-      <c r="F20" s="2">
-        <v>150</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="I20" s="2" t="e">
         <f>1/0</f>
@@ -2532,17 +2532,17 @@
       <c r="D21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="2">
+        <v>150</v>
+      </c>
+      <c r="H21" s="2">
         <v>1150</v>
-      </c>
-      <c r="F21" s="2">
-        <v>150</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I21" s="2">
         <v>0.1304347826086956</v>
@@ -2561,17 +2561,17 @@
       <c r="D22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2">
         <v>0</v>
       </c>
-      <c r="F22" s="2">
+      <c r="H22" s="2">
         <v>0</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="I22" s="2" t="e">
         <f>#NUM!</f>
@@ -2591,17 +2591,17 @@
       <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2">
         <v>1150</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
@@ -2620,17 +2620,17 @@
       <c r="D24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2">
         <v>1E-07</v>
       </c>
-      <c r="F24" s="2">
+      <c r="H24" s="2">
         <v>1E-07</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
@@ -2649,17 +2649,17 @@
       <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1E-07</v>
+      </c>
+      <c r="H25" s="2">
         <v>1000</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1E-07</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I25" s="2">
         <v>9.999999999999999E-11</v>
@@ -2678,17 +2678,17 @@
       <c r="D26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1E-07</v>
+      </c>
+      <c r="H26" s="2">
         <v>1000</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1E-07</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="I26" s="2">
         <v>9.999999999999999E-11</v>
@@ -2707,16 +2707,16 @@
       <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2">
+      <c r="E27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2">
         <v>1E-07</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9">
@@ -2732,16 +2732,16 @@
       <c r="D28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2">
+      <c r="E28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
         <v>1E-07</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9">
@@ -2757,17 +2757,17 @@
       <c r="D29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
         <v>160</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="I29" s="2">
         <v>0</v>
@@ -2786,15 +2786,15 @@
       <c r="D30" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2">
         <v>160</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="I30" s="2"/>
     </row>
@@ -2811,15 +2811,15 @@
       <c r="D31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2">
         <v>0</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="I31" s="2"/>
     </row>
